--- a/tests/test-cases.xlsx
+++ b/tests/test-cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="169">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -64,7 +64,10 @@
     <t>Home page loads and main navigation is visible</t>
   </si>
   <si>
-    <t>Not Run</t>
+    <t>Home page opened successfully. Main navigation and advertisement slider were visible and working correctly. Product cards loaded after a short delay of approximately 1–3 seconds, with a slight visible loading lag. Product cards loaded after more than 3 seconds during testing on 02/07/2026 at 11:19.</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>High</t>
@@ -88,6 +91,9 @@
     <t>Product images, names and prices are visible</t>
   </si>
   <si>
+    <t>Product cards were displayed successfully. Product names, prices and descriptions were visible. However, some laptop products appear to use the same or very similar images, for example MacBook Air and MacBook Pro, Dell i7 6500U and Dell i7 7500U, and Sony Vaio i5 and Sony Vaio i7. This may confuse users when comparing products.</t>
+  </si>
+  <si>
     <t>TC-003</t>
   </si>
   <si>
@@ -103,6 +109,12 @@
     <t>Only phone products are displayed</t>
   </si>
   <si>
+    <t>After clicking the Phones category, only phone products were displayed. Product names, prices and descriptions were visible. Samsung Galaxy S6 and Samsung Galaxy S7 appear to use the same or very similar product image, which may be a content/usability issue. The Previous pagination button remained visible in the Phones category. When clicking Previous, the user was redirected back to the main product list instead of staying inside the selected Phones category. Also when choose Phones category, its not highlighted, so user cannot understand where he is.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -121,6 +133,9 @@
     <t>Only laptop products are displayed</t>
   </si>
   <si>
+    <t>After clicking the Laptops category, 6 laptop products were displayed. Product names, prices and descriptions were visible. However, several laptop products use duplicate or very similar images: both Dell laptops use the same image, both Sony Vaio laptops use the same image, and both MacBook products use the same image. The Next and Previous pagination buttons remained visible in the Laptops category. When clicking the pagination buttons, the user was redirected back to the main product list instead of staying inside the selected Laptops category.</t>
+  </si>
+  <si>
     <t>TC-005</t>
   </si>
   <si>
@@ -136,6 +151,9 @@
     <t>Only monitor products are displayed</t>
   </si>
   <si>
+    <t>After clicking the Monitors category, only monitor products were displayed. Product names, prices and descriptions were visible. Product images were different and no duplicate image issue was observed for monitor products. However, the Next and Previous pagination buttons remained visible in the Monitors category. When clicking the pagination buttons, the user was redirected back to the main product list instead of staying inside the selected Monitors category.</t>
+  </si>
+  <si>
     <t>TC-006</t>
   </si>
   <si>
@@ -154,6 +172,9 @@
     <t>Product detail page opens with name, image, price and description</t>
   </si>
   <si>
+    <t>Product detail page opened successfully after clicking Samsung galaxy s6. Product name, image, price and description were visible. However, the page loaded slowly, approximately 4–6 seconds. Product title capitalization is inconsistent: the product is displayed as “Samsung galaxy s6” instead of “Samsung Galaxy S6”.</t>
+  </si>
+  <si>
     <t>TC-007</t>
   </si>
   <si>
@@ -172,6 +193,9 @@
     <t>Product is added to cart and confirmation message appears</t>
   </si>
   <si>
+    <t>After clicking “Add to cart” on the product detail page, a browser alert message appeared with the text “Product added”. The confirmation message was displayed successfully. Cart contents were not verified in this test case because cart verification is covered in TC-008.</t>
+  </si>
+  <si>
     <t>TC-008</t>
   </si>
   <si>
@@ -190,6 +214,9 @@
     <t>Cart page shows added product with price</t>
   </si>
   <si>
+    <t>The added product appeared in the cart successfully. Product image, title, price, Delete option, total price and Place Order button were visible. The total price matched the product price. The cart page layout looks visually unpolished, with a lot of empty space and basic table styling, but the main cart functionality worked correctly.</t>
+  </si>
+  <si>
     <t>TC-009</t>
   </si>
   <si>
@@ -205,6 +232,9 @@
     <t>Product is removed from cart</t>
   </si>
   <si>
+    <t>After clicking “Delete”, the product was removed from the cart successfully. During an earlier test attempt, a temporary delay was observed when adding new products after deleting an item, but the issue was not reproduced during retesting.</t>
+  </si>
+  <si>
     <t>TC-010</t>
   </si>
   <si>
@@ -217,6 +247,10 @@
     <t>Order form modal opens</t>
   </si>
   <si>
+    <t xml:space="preserve">After clicking “Place Order”, the order form modal opened successfully. The modal displayed the total price and input fields for Name, Country, City, Credit card, Month and Year. At 100% browser zoom, the modal was too large for the visible screen area and required scrolling to access the lower part of the form and action buttons. At 80% zoom, the modal looked more properly fitted. The form includes credit card, month and year fields, but does not include a card security code / CVV field. This may be a payment form completeness issue if the form is intended to simulate a real card payment process.
+</t>
+  </si>
+  <si>
     <t>TC-011</t>
   </si>
   <si>
@@ -235,6 +269,9 @@
     <t>Purchase is completed and confirmation message appears</t>
   </si>
   <si>
+    <t>After filling in all Place Order form fields and clicking “Purchase”, a confirmation window appeared with the entered order data. After clicking “OK”, the user was redirected back to the home page and the cart was cleared. During additional testing, it was observed that the form accepts any text values in payment-related fields and does not validate credit card, month or year format.</t>
+  </si>
+  <si>
     <t>TC-012</t>
   </si>
   <si>
@@ -250,6 +287,9 @@
     <t>System should show validation or prevent purchase</t>
   </si>
   <si>
+    <t xml:space="preserve">When the Place Order form fields were left empty and the user clicked “Purchase”, the system did not complete the order. The checkout flow was blocked until required fields were filled in. A validation alert was displayed: “Please fill out Name and Creditcard.” </t>
+  </si>
+  <si>
     <t>TC-013</t>
   </si>
   <si>
@@ -262,6 +302,9 @@
     <t>Click “Sign up”</t>
   </si>
   <si>
+    <t>After clicking “Sign up”, the sign up modal opened successfully. The modal displayed fields for username and password, and the user was able to enter text into both fields. When user types password, its protected by default ****</t>
+  </si>
+  <si>
     <t>TC-014</t>
   </si>
   <si>
@@ -280,6 +323,9 @@
     <t>User account is created or confirmation appears</t>
   </si>
   <si>
+    <t>After entering a unique username and password and clicking “Sign up”, the website displayed a confirmation message successfully. During an earlier test attempt, the confirmation message appeared delayed, but the issue was not reproduced during retesting.</t>
+  </si>
+  <si>
     <t>TC-015</t>
   </si>
   <si>
@@ -295,6 +341,9 @@
     <t>System should show validation or prevent sign up</t>
   </si>
   <si>
+    <t>After clicking “Sign up” with empty username and password fields, the website immediately displayed an error message: “Please fill out Username and Password.”</t>
+  </si>
+  <si>
     <t>TC-016</t>
   </si>
   <si>
@@ -307,6 +356,9 @@
     <t>Login modal opens</t>
   </si>
   <si>
+    <t>After clicking "Login", the login modal opened successfully. The Modal displayed fields for username and password, and the user was able to enter text into both fields.</t>
+  </si>
+  <si>
     <t>TC-017</t>
   </si>
   <si>
@@ -325,6 +377,9 @@
     <t>User is logged in and username is visible</t>
   </si>
   <si>
+    <t>After entering a valid username and password and clicking “Log in”, the user was logged in successfully. The navigation updated and displayed “Welcome [username]”. During earlier testing, login feedback appeared delayed, but the issue was not consistently reproduced during retesting.</t>
+  </si>
+  <si>
     <t>TC-018</t>
   </si>
   <si>
@@ -343,6 +398,9 @@
     <t>Error message appears</t>
   </si>
   <si>
+    <t>After entering invalid login credentials and clicking “Log in”, the website displayed an error message: “User does not exist.”</t>
+  </si>
+  <si>
     <t>TC-019</t>
   </si>
   <si>
@@ -358,6 +416,9 @@
     <t>User is logged out and login/sign up options appear</t>
   </si>
   <si>
+    <t>After clicking “Log out”, the page refreshed and the user was logged out successfully. The navigation returned to the logged-out state and displayed “Sign up” and “Log in” options again.</t>
+  </si>
+  <si>
     <t>TC-020</t>
   </si>
   <si>
@@ -370,6 +431,9 @@
     <t>Contact form modal opens</t>
   </si>
   <si>
+    <t>After clicking “Contact”, the contact form modal opened successfully. The modal displayed fields for Contact Email, Contact Name and Message. The Close and Send message buttons were visible.</t>
+  </si>
+  <si>
     <t>TC-021</t>
   </si>
   <si>
@@ -388,6 +452,9 @@
     <t>Message is sent or confirmation appears</t>
   </si>
   <si>
+    <t>After filling in Contact Email, Contact Name and Message fields and clicking “Send message”, the website displayed a confirmation message: “Thanks for the message!!”</t>
+  </si>
+  <si>
     <t>TC-022</t>
   </si>
   <si>
@@ -400,6 +467,9 @@
     <t>System should show validation or prevent sending</t>
   </si>
   <si>
+    <t>After leaving Contact Email, Contact Name and Message fields empty and clicking “Send message”, the website still displayed a confirmation message: “Thanks for the message!!”. The form was submitted without validating required fields.</t>
+  </si>
+  <si>
     <t>TC-023</t>
   </si>
   <si>
@@ -412,6 +482,9 @@
     <t>About us modal opens with video/content area</t>
   </si>
   <si>
+    <t>After clicking “About us”, the About us modal opened successfully. The modal displayed a video/content area and the user was able to access the video.</t>
+  </si>
+  <si>
     <t>Low</t>
   </si>
   <si>
@@ -430,6 +503,9 @@
     <t>User returns to home page</t>
   </si>
   <si>
+    <t>After opening the Cart page and clicking “Home” in the navigation menu, the user was redirected back to the main page successfully.</t>
+  </si>
+  <si>
     <t>TC-025</t>
   </si>
   <si>
@@ -446,6 +522,9 @@
   </si>
   <si>
     <t>Total price equals sum of product prices</t>
+  </si>
+  <si>
+    <t>After adding two products to the cart, one priced at 800 and another priced at 400, the cart total was displayed as 1200. The total price was calculated correctly.</t>
   </si>
 </sst>
 </file>
@@ -489,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -504,9 +583,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -725,7 +801,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="9" width="18.88"/>
+    <col customWidth="1" min="1" max="1" width="8.63"/>
+    <col customWidth="1" min="2" max="3" width="27.5"/>
+    <col customWidth="1" min="4" max="4" width="31.38"/>
+    <col customWidth="1" min="5" max="5" width="24.13"/>
+    <col customWidth="1" min="6" max="9" width="31.38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,660 +856,710 @@
       <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="5"/>
+        <v>29</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>44</v>
+      </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="5"/>
+        <v>50</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="5"/>
+        <v>57</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="5"/>
+        <v>64</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="5"/>
+        <v>82</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="5"/>
+        <v>88</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="5"/>
+        <v>106</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="5"/>
+        <v>111</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="5"/>
+        <v>118</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>125</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="5"/>
+        <v>131</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>132</v>
+      </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G21" s="5"/>
+        <v>136</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="5"/>
+        <v>143</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>144</v>
+      </c>
       <c r="H22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" s="5"/>
+        <v>148</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="H23" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G24" s="5"/>
+        <v>153</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>154</v>
+      </c>
       <c r="H24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="5"/>
+        <v>160</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>161</v>
+      </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G26" s="5"/>
+        <v>167</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>168</v>
+      </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
